--- a/assets/PLANTILLA_SECUNDARIA.xlsx
+++ b/assets/PLANTILLA_SECUNDARIA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kioskUser0\OneDrive\Escritorio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kioskUser0\OneDrive\Escritorio\generador-libretas-main\generador-libretas-main\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E6CBCEB-8C8F-417D-96B4-D1706F5A1766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{046AF800-7B67-4D89-8514-CE91F901C9E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,8 +34,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -486,13 +484,13 @@
     <t>NIVEL SECUNDARIA 2026</t>
   </si>
   <si>
-    <t>I BIMESTRE</t>
-  </si>
-  <si>
     <t>5° AÑO</t>
   </si>
   <si>
     <t>JOSE LUIS CHOQUEGONZA MAMANI</t>
+  </si>
+  <si>
+    <t>II BIMESTRE</t>
   </si>
 </sst>
 </file>
@@ -1450,8 +1448,84 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1493,100 +1567,11 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1596,6 +1581,19 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11526,24 +11524,24 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9" ht="18.75">
-      <c r="A2" s="104" t="s">
+      <c r="A2" s="88" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="104"/>
-      <c r="C2" s="104"/>
-      <c r="D2" s="104"/>
-      <c r="E2" s="104"/>
-      <c r="F2" s="104"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="105" t="s">
+      <c r="A3" s="89" t="s">
         <v>146</v>
       </c>
-      <c r="B3" s="105"/>
-      <c r="C3" s="105"/>
-      <c r="D3" s="105"/>
-      <c r="E3" s="105"/>
-      <c r="F3" s="105"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
     </row>
@@ -11551,10 +11549,10 @@
       <c r="C5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="111" t="s">
-        <v>148</v>
-      </c>
-      <c r="E5" s="111"/>
+      <c r="D5" s="95" t="s">
+        <v>147</v>
+      </c>
+      <c r="E5" s="95"/>
       <c r="I5" s="5"/>
     </row>
     <row r="6" spans="1:9">
@@ -11574,7 +11572,7 @@
         <v>SULLCA CHIPANA JULIO CESAR MATIAS</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.75" thickBot="1">
@@ -11582,25 +11580,25 @@
         <v>119</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="B9" s="108" t="s">
+      <c r="B9" s="92" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="106" t="s">
+      <c r="C9" s="90" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="106" t="s">
+      <c r="D9" s="90" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="106"/>
-      <c r="F9" s="107"/>
+      <c r="E9" s="90"/>
+      <c r="F9" s="91"/>
     </row>
     <row r="10" spans="1:9" ht="15.75" thickBot="1">
-      <c r="B10" s="109"/>
-      <c r="C10" s="110"/>
+      <c r="B10" s="93"/>
+      <c r="C10" s="94"/>
       <c r="D10" s="50" t="s">
         <v>20</v>
       </c>
@@ -11612,7 +11610,7 @@
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="B11" s="112" t="s">
+      <c r="B11" s="83" t="s">
         <v>61</v>
       </c>
       <c r="C11" s="7" t="s">
@@ -11632,7 +11630,7 @@
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="B12" s="113"/>
+      <c r="B12" s="84"/>
       <c r="C12" s="9" t="s">
         <v>60</v>
       </c>
@@ -11650,7 +11648,7 @@
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="B13" s="113"/>
+      <c r="B13" s="84"/>
       <c r="C13" s="9" t="s">
         <v>59</v>
       </c>
@@ -11668,7 +11666,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="15.75" thickBot="1">
-      <c r="B14" s="113"/>
+      <c r="B14" s="84"/>
       <c r="C14" s="10" t="s">
         <v>144</v>
       </c>
@@ -11686,7 +11684,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1">
-      <c r="B15" s="112" t="s">
+      <c r="B15" s="83" t="s">
         <v>98</v>
       </c>
       <c r="C15" s="7" t="s">
@@ -11706,7 +11704,7 @@
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="B16" s="113"/>
+      <c r="B16" s="84"/>
       <c r="C16" s="9" t="s">
         <v>127</v>
       </c>
@@ -11724,7 +11722,7 @@
       </c>
     </row>
     <row r="17" spans="2:6" ht="15.75" thickBot="1">
-      <c r="B17" s="113"/>
+      <c r="B17" s="84"/>
       <c r="C17" s="11" t="s">
         <v>128</v>
       </c>
@@ -11742,7 +11740,7 @@
       </c>
     </row>
     <row r="18" spans="2:6">
-      <c r="B18" s="112" t="s">
+      <c r="B18" s="83" t="s">
         <v>124</v>
       </c>
       <c r="C18" s="12" t="s">
@@ -11762,7 +11760,7 @@
       </c>
     </row>
     <row r="19" spans="2:6">
-      <c r="B19" s="113"/>
+      <c r="B19" s="84"/>
       <c r="C19" s="9" t="s">
         <v>51</v>
       </c>
@@ -11780,7 +11778,7 @@
       </c>
     </row>
     <row r="20" spans="2:6" ht="15.75" thickBot="1">
-      <c r="B20" s="113"/>
+      <c r="B20" s="84"/>
       <c r="C20" s="10" t="s">
         <v>130</v>
       </c>
@@ -11798,7 +11796,7 @@
       </c>
     </row>
     <row r="21" spans="2:6" ht="17.25" customHeight="1">
-      <c r="B21" s="94" t="s">
+      <c r="B21" s="85" t="s">
         <v>145</v>
       </c>
       <c r="C21" s="7" t="s">
@@ -11818,7 +11816,7 @@
       </c>
     </row>
     <row r="22" spans="2:6" ht="18" customHeight="1" thickBot="1">
-      <c r="B22" s="96"/>
+      <c r="B22" s="87"/>
       <c r="C22" s="11" t="s">
         <v>102</v>
       </c>
@@ -11836,7 +11834,7 @@
       </c>
     </row>
     <row r="23" spans="2:6">
-      <c r="B23" s="95" t="s">
+      <c r="B23" s="86" t="s">
         <v>57</v>
       </c>
       <c r="C23" s="7" t="s">
@@ -11856,7 +11854,7 @@
       </c>
     </row>
     <row r="24" spans="2:6" ht="15.75" thickBot="1">
-      <c r="B24" s="96"/>
+      <c r="B24" s="87"/>
       <c r="C24" s="11" t="s">
         <v>56</v>
       </c>
@@ -11874,7 +11872,7 @@
       </c>
     </row>
     <row r="25" spans="2:6">
-      <c r="B25" s="94" t="s">
+      <c r="B25" s="85" t="s">
         <v>54</v>
       </c>
       <c r="C25" s="7" t="s">
@@ -11894,7 +11892,7 @@
       </c>
     </row>
     <row r="26" spans="2:6">
-      <c r="B26" s="95"/>
+      <c r="B26" s="86"/>
       <c r="C26" s="9" t="s">
         <v>50</v>
       </c>
@@ -11912,7 +11910,7 @@
       </c>
     </row>
     <row r="27" spans="2:6" ht="15.75" thickBot="1">
-      <c r="B27" s="96"/>
+      <c r="B27" s="87"/>
       <c r="C27" s="11" t="s">
         <v>53</v>
       </c>
@@ -11930,7 +11928,7 @@
       </c>
     </row>
     <row r="28" spans="2:6" ht="15" customHeight="1">
-      <c r="B28" s="94" t="s">
+      <c r="B28" s="85" t="s">
         <v>63</v>
       </c>
       <c r="C28" s="7" t="s">
@@ -11950,7 +11948,7 @@
       </c>
     </row>
     <row r="29" spans="2:6" ht="26.25">
-      <c r="B29" s="95"/>
+      <c r="B29" s="86"/>
       <c r="C29" s="13" t="s">
         <v>143</v>
       </c>
@@ -11968,7 +11966,7 @@
       </c>
     </row>
     <row r="30" spans="2:6" ht="15.75" thickBot="1">
-      <c r="B30" s="96"/>
+      <c r="B30" s="87"/>
       <c r="C30" s="11" t="s">
         <v>142</v>
       </c>
@@ -11986,7 +11984,7 @@
       </c>
     </row>
     <row r="31" spans="2:6" ht="15" customHeight="1">
-      <c r="B31" s="94" t="s">
+      <c r="B31" s="85" t="s">
         <v>125</v>
       </c>
       <c r="C31" s="7" t="s">
@@ -12006,7 +12004,7 @@
       </c>
     </row>
     <row r="32" spans="2:6">
-      <c r="B32" s="95"/>
+      <c r="B32" s="86"/>
       <c r="C32" s="9" t="s">
         <v>140</v>
       </c>
@@ -12024,7 +12022,7 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="15.75" thickBot="1">
-      <c r="B33" s="96"/>
+      <c r="B33" s="87"/>
       <c r="C33" s="11" t="s">
         <v>139</v>
       </c>
@@ -12042,7 +12040,7 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="39">
-      <c r="B34" s="94" t="s">
+      <c r="B34" s="85" t="s">
         <v>64</v>
       </c>
       <c r="C34" s="53" t="s">
@@ -12062,7 +12060,7 @@
       </c>
     </row>
     <row r="35" spans="2:6" ht="27" thickBot="1">
-      <c r="B35" s="95"/>
+      <c r="B35" s="86"/>
       <c r="C35" s="14" t="s">
         <v>138</v>
       </c>
@@ -12140,13 +12138,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="94" t="s">
+      <c r="B39" s="85" t="s">
         <v>71</v>
       </c>
-      <c r="C39" s="97" t="s">
+      <c r="C39" s="96" t="s">
         <v>69</v>
       </c>
-      <c r="D39" s="97"/>
+      <c r="D39" s="96"/>
       <c r="E39" s="99" t="str">
         <f>IFERROR(VLOOKUP($C$6,CONSOLIDADO!$A$1:$EF$33,CONSOLIDADO!$CI$1,0),"-")</f>
         <v>A</v>
@@ -12154,11 +12152,11 @@
       <c r="F39" s="100"/>
     </row>
     <row r="40" spans="2:6" ht="15.75" thickBot="1">
-      <c r="B40" s="96"/>
-      <c r="C40" s="98" t="s">
+      <c r="B40" s="87"/>
+      <c r="C40" s="97" t="s">
         <v>70</v>
       </c>
-      <c r="D40" s="98"/>
+      <c r="D40" s="97"/>
       <c r="E40" s="101" t="str">
         <f>IFERROR(VLOOKUP($C$6,CONSOLIDADO!$A$1:$EF$33,CONSOLIDADO!$CJ$1,0),"-")</f>
         <v>A</v>
@@ -12167,10 +12165,10 @@
     </row>
     <row r="41" spans="2:6" ht="15.75" thickBot="1"/>
     <row r="42" spans="2:6" ht="31.5" customHeight="1">
-      <c r="B42" s="84" t="s">
+      <c r="B42" s="104" t="s">
         <v>48</v>
       </c>
-      <c r="C42" s="85"/>
+      <c r="C42" s="105"/>
       <c r="D42" s="16" t="s">
         <v>72</v>
       </c>
@@ -12362,16 +12360,16 @@
       </c>
     </row>
     <row r="52" spans="2:6" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B52" s="88" t="s">
+      <c r="B52" s="108" t="s">
         <v>75</v>
       </c>
-      <c r="C52" s="89"/>
+      <c r="C52" s="109"/>
       <c r="D52" s="41" t="str">
         <f>IFERROR(VLOOKUP($C$6,CONSOLIDADO!$A$1:$EF$33,CONSOLIDADO!$DL$1,0),"-")</f>
         <v>A</v>
       </c>
-      <c r="E52" s="86"/>
-      <c r="F52" s="87"/>
+      <c r="E52" s="106"/>
+      <c r="F52" s="107"/>
     </row>
     <row r="53" spans="2:6" ht="18.75" customHeight="1">
       <c r="B53" s="23"/>
@@ -12436,10 +12434,10 @@
       </c>
     </row>
     <row r="65" spans="2:6" ht="31.5" customHeight="1">
-      <c r="B65" s="90" t="s">
+      <c r="B65" s="110" t="s">
         <v>78</v>
       </c>
-      <c r="C65" s="90"/>
+      <c r="C65" s="110"/>
       <c r="D65" s="26" t="s">
         <v>76</v>
       </c>
@@ -12534,50 +12532,50 @@
       <c r="C70" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="D70" s="91" t="str">
+      <c r="D70" s="111" t="str">
         <f>IFERROR(VLOOKUP($C$6,CONSOLIDADO!$A$1:$EF$33,CONSOLIDADO!$DY$1,0),"-")</f>
         <v>A</v>
       </c>
-      <c r="E70" s="91" t="str">
+      <c r="E70" s="111" t="str">
         <f>IFERROR(VLOOKUP($C$6,CONSOLIDADO!$A$1:$EF$33,CONSOLIDADO!#REF!,0),"-")</f>
         <v>-</v>
       </c>
       <c r="F70" s="31"/>
     </row>
     <row r="72" spans="2:6">
-      <c r="B72" s="93" t="s">
+      <c r="B72" s="113" t="s">
         <v>88</v>
       </c>
-      <c r="C72" s="93"/>
-      <c r="D72" s="93"/>
-      <c r="E72" s="93"/>
-      <c r="F72" s="93"/>
+      <c r="C72" s="113"/>
+      <c r="D72" s="113"/>
+      <c r="E72" s="113"/>
+      <c r="F72" s="113"/>
     </row>
     <row r="73" spans="2:6">
       <c r="B73" s="103">
         <v>1</v>
       </c>
-      <c r="C73" s="92" t="str">
+      <c r="C73" s="112" t="str">
         <f>IFERROR(VLOOKUP($C$6,CONSOLIDADO!$A$1:$EF$33,CONSOLIDADO!$EF$1,0),"-")</f>
         <v>El estudiante muestra iniciativa para la colaboración en actividades, debe de mantener reforzando lo que avanza en clase y sus tareas.</v>
       </c>
-      <c r="D73" s="92"/>
-      <c r="E73" s="92"/>
-      <c r="F73" s="92"/>
+      <c r="D73" s="112"/>
+      <c r="E73" s="112"/>
+      <c r="F73" s="112"/>
     </row>
     <row r="74" spans="2:6">
       <c r="B74" s="103"/>
-      <c r="C74" s="92"/>
-      <c r="D74" s="92"/>
-      <c r="E74" s="92"/>
-      <c r="F74" s="92"/>
+      <c r="C74" s="112"/>
+      <c r="D74" s="112"/>
+      <c r="E74" s="112"/>
+      <c r="F74" s="112"/>
     </row>
     <row r="75" spans="2:6">
       <c r="B75" s="103"/>
-      <c r="C75" s="92"/>
-      <c r="D75" s="92"/>
-      <c r="E75" s="92"/>
-      <c r="F75" s="92"/>
+      <c r="C75" s="112"/>
+      <c r="D75" s="112"/>
+      <c r="E75" s="112"/>
+      <c r="F75" s="112"/>
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="32"/>
@@ -12587,25 +12585,47 @@
       <c r="F76" s="33"/>
     </row>
     <row r="80" spans="2:6">
-      <c r="B80" s="83" t="s">
+      <c r="B80" s="98" t="s">
         <v>96</v>
       </c>
-      <c r="C80" s="83"/>
-      <c r="D80" s="83"/>
-      <c r="E80" s="83"/>
-      <c r="F80" s="83"/>
+      <c r="C80" s="98"/>
+      <c r="D80" s="98"/>
+      <c r="E80" s="98"/>
+      <c r="F80" s="98"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="83" t="s">
+      <c r="B81" s="98" t="s">
         <v>95</v>
       </c>
-      <c r="C81" s="83"/>
-      <c r="D81" s="83"/>
-      <c r="E81" s="83"/>
-      <c r="F81" s="83"/>
+      <c r="C81" s="98"/>
+      <c r="D81" s="98"/>
+      <c r="E81" s="98"/>
+      <c r="F81" s="98"/>
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="C73:F75"/>
+    <mergeCell ref="B72:F72"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="B73:B75"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D5:E5"/>
     <mergeCell ref="B18:B20"/>
     <mergeCell ref="B31:B33"/>
     <mergeCell ref="B11:B14"/>
@@ -12614,28 +12634,6 @@
     <mergeCell ref="B25:B27"/>
     <mergeCell ref="B23:B24"/>
     <mergeCell ref="B28:B30"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="B80:F80"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="B73:B75"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="C73:F75"/>
-    <mergeCell ref="B72:F72"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="92" orientation="portrait" r:id="rId1"/>
@@ -13196,10 +13194,10 @@
       </c>
       <c r="CG2" s="115"/>
       <c r="CH2" s="116"/>
-      <c r="CI2" s="123" t="s">
+      <c r="CI2" s="118" t="s">
         <v>47</v>
       </c>
-      <c r="CJ2" s="124"/>
+      <c r="CJ2" s="119"/>
       <c r="CK2" s="114" t="s">
         <v>106</v>
       </c>
@@ -13256,7 +13254,7 @@
       <c r="EF2" s="72" t="s">
         <v>120</v>
       </c>
-      <c r="EG2" s="122" t="s">
+      <c r="EG2" s="117" t="s">
         <v>121</v>
       </c>
       <c r="EH2" s="116"/>
@@ -13408,14 +13406,14 @@
       </c>
       <c r="CG3" s="115"/>
       <c r="CH3" s="116"/>
-      <c r="CI3" s="125"/>
-      <c r="CJ3" s="126"/>
+      <c r="CI3" s="120"/>
+      <c r="CJ3" s="121"/>
       <c r="CK3" s="114">
         <v>1</v>
       </c>
       <c r="CL3" s="115"/>
       <c r="CM3" s="116"/>
-      <c r="CN3" s="117">
+      <c r="CN3" s="124">
         <v>2</v>
       </c>
       <c r="CO3" s="115"/>
@@ -13425,12 +13423,12 @@
       </c>
       <c r="CR3" s="115"/>
       <c r="CS3" s="116"/>
-      <c r="CT3" s="117">
+      <c r="CT3" s="124">
         <v>4</v>
       </c>
       <c r="CU3" s="115"/>
       <c r="CV3" s="116"/>
-      <c r="CW3" s="117">
+      <c r="CW3" s="124">
         <v>5</v>
       </c>
       <c r="CX3" s="115"/>
@@ -13440,7 +13438,7 @@
       </c>
       <c r="DA3" s="115"/>
       <c r="DB3" s="116"/>
-      <c r="DC3" s="117">
+      <c r="DC3" s="124">
         <v>7</v>
       </c>
       <c r="DD3" s="115"/>
@@ -13455,7 +13453,7 @@
       </c>
       <c r="DJ3" s="115"/>
       <c r="DK3" s="116"/>
-      <c r="DL3" s="120" t="s">
+      <c r="DL3" s="126" t="s">
         <v>113</v>
       </c>
       <c r="DM3" s="114">
@@ -13463,7 +13461,7 @@
       </c>
       <c r="DN3" s="115"/>
       <c r="DO3" s="116"/>
-      <c r="DP3" s="117">
+      <c r="DP3" s="124">
         <v>2</v>
       </c>
       <c r="DQ3" s="115"/>
@@ -13473,35 +13471,35 @@
       </c>
       <c r="DT3" s="115"/>
       <c r="DU3" s="116"/>
-      <c r="DV3" s="117">
+      <c r="DV3" s="124">
         <v>4</v>
       </c>
       <c r="DW3" s="115"/>
       <c r="DX3" s="116"/>
       <c r="DY3" s="75"/>
-      <c r="DZ3" s="121" t="s">
+      <c r="DZ3" s="122" t="s">
         <v>114</v>
       </c>
-      <c r="EA3" s="120" t="s">
+      <c r="EA3" s="126" t="s">
         <v>115</v>
       </c>
-      <c r="EB3" s="121" t="s">
+      <c r="EB3" s="122" t="s">
         <v>49</v>
       </c>
-      <c r="EC3" s="121" t="s">
+      <c r="EC3" s="122" t="s">
         <v>116</v>
       </c>
-      <c r="ED3" s="121" t="s">
+      <c r="ED3" s="122" t="s">
         <v>117</v>
       </c>
-      <c r="EE3" s="121" t="s">
+      <c r="EE3" s="122" t="s">
         <v>118</v>
       </c>
       <c r="EF3" s="76"/>
-      <c r="EG3" s="118" t="s">
+      <c r="EG3" s="125" t="s">
         <v>122</v>
       </c>
-      <c r="EH3" s="118" t="s">
+      <c r="EH3" s="125" t="s">
         <v>123</v>
       </c>
     </row>
@@ -13847,7 +13845,7 @@
       <c r="DK4" s="77" t="s">
         <v>77</v>
       </c>
-      <c r="DL4" s="119"/>
+      <c r="DL4" s="123"/>
       <c r="DM4" s="77" t="s">
         <v>76</v>
       </c>
@@ -13887,15 +13885,15 @@
       <c r="DY4" s="77" t="s">
         <v>113</v>
       </c>
-      <c r="DZ4" s="119"/>
-      <c r="EA4" s="119"/>
-      <c r="EB4" s="119"/>
-      <c r="EC4" s="119"/>
-      <c r="ED4" s="119"/>
-      <c r="EE4" s="119"/>
+      <c r="DZ4" s="123"/>
+      <c r="EA4" s="123"/>
+      <c r="EB4" s="123"/>
+      <c r="EC4" s="123"/>
+      <c r="ED4" s="123"/>
+      <c r="EE4" s="123"/>
       <c r="EF4" s="78"/>
-      <c r="EG4" s="119"/>
-      <c r="EH4" s="119"/>
+      <c r="EG4" s="123"/>
+      <c r="EH4" s="123"/>
     </row>
     <row r="5" spans="1:141">
       <c r="A5" s="56" t="s">
@@ -30539,28 +30537,35 @@
     <row r="1000" customFormat="1" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="67">
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="O3:Q3"/>
-    <mergeCell ref="R3:T3"/>
-    <mergeCell ref="U3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="AA3:AC3"/>
-    <mergeCell ref="AD3:AF3"/>
-    <mergeCell ref="BB3:BD3"/>
-    <mergeCell ref="BE3:BG3"/>
-    <mergeCell ref="BH3:BJ3"/>
-    <mergeCell ref="BN3:BP3"/>
-    <mergeCell ref="BQ3:BS3"/>
-    <mergeCell ref="AV3:AX3"/>
-    <mergeCell ref="AY3:BA3"/>
-    <mergeCell ref="AG3:AI3"/>
-    <mergeCell ref="AJ3:AL3"/>
-    <mergeCell ref="AM3:AO3"/>
-    <mergeCell ref="AP3:AR3"/>
-    <mergeCell ref="AS3:AU3"/>
+    <mergeCell ref="DS3:DU3"/>
+    <mergeCell ref="CK3:CM3"/>
+    <mergeCell ref="CN3:CP3"/>
+    <mergeCell ref="CQ3:CS3"/>
+    <mergeCell ref="BK2:BS2"/>
+    <mergeCell ref="BT2:BY2"/>
+    <mergeCell ref="BZ2:CB2"/>
+    <mergeCell ref="CC2:CE2"/>
+    <mergeCell ref="CF2:CH2"/>
+    <mergeCell ref="BW3:BY3"/>
+    <mergeCell ref="CT3:CV3"/>
+    <mergeCell ref="CW3:CY3"/>
+    <mergeCell ref="BT3:BV3"/>
+    <mergeCell ref="DZ2:EE2"/>
+    <mergeCell ref="EG3:EG4"/>
+    <mergeCell ref="EH3:EH4"/>
+    <mergeCell ref="BZ3:CB3"/>
+    <mergeCell ref="CC3:CE3"/>
+    <mergeCell ref="DL3:DL4"/>
+    <mergeCell ref="DZ3:DZ4"/>
+    <mergeCell ref="EA3:EA4"/>
+    <mergeCell ref="EB3:EB4"/>
+    <mergeCell ref="EC3:EC4"/>
+    <mergeCell ref="CZ3:DB3"/>
+    <mergeCell ref="DC3:DE3"/>
+    <mergeCell ref="DF3:DH3"/>
+    <mergeCell ref="DI3:DK3"/>
+    <mergeCell ref="DM3:DO3"/>
+    <mergeCell ref="DP3:DR3"/>
     <mergeCell ref="EG2:EH2"/>
     <mergeCell ref="C2:N2"/>
     <mergeCell ref="O2:W2"/>
@@ -30577,35 +30582,28 @@
     <mergeCell ref="CK2:DL2"/>
     <mergeCell ref="DM2:DY2"/>
     <mergeCell ref="DV3:DX3"/>
-    <mergeCell ref="DZ2:EE2"/>
-    <mergeCell ref="EG3:EG4"/>
-    <mergeCell ref="EH3:EH4"/>
-    <mergeCell ref="BZ3:CB3"/>
-    <mergeCell ref="CC3:CE3"/>
-    <mergeCell ref="DL3:DL4"/>
-    <mergeCell ref="DZ3:DZ4"/>
-    <mergeCell ref="EA3:EA4"/>
-    <mergeCell ref="EB3:EB4"/>
-    <mergeCell ref="EC3:EC4"/>
-    <mergeCell ref="CZ3:DB3"/>
-    <mergeCell ref="DC3:DE3"/>
-    <mergeCell ref="DF3:DH3"/>
-    <mergeCell ref="DI3:DK3"/>
-    <mergeCell ref="DM3:DO3"/>
-    <mergeCell ref="DP3:DR3"/>
-    <mergeCell ref="DS3:DU3"/>
-    <mergeCell ref="CK3:CM3"/>
-    <mergeCell ref="CN3:CP3"/>
-    <mergeCell ref="CQ3:CS3"/>
-    <mergeCell ref="BK2:BS2"/>
-    <mergeCell ref="BT2:BY2"/>
-    <mergeCell ref="BZ2:CB2"/>
-    <mergeCell ref="CC2:CE2"/>
-    <mergeCell ref="CF2:CH2"/>
-    <mergeCell ref="BW3:BY3"/>
-    <mergeCell ref="CT3:CV3"/>
-    <mergeCell ref="CW3:CY3"/>
-    <mergeCell ref="BT3:BV3"/>
+    <mergeCell ref="AV3:AX3"/>
+    <mergeCell ref="AY3:BA3"/>
+    <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="AJ3:AL3"/>
+    <mergeCell ref="AM3:AO3"/>
+    <mergeCell ref="AP3:AR3"/>
+    <mergeCell ref="AS3:AU3"/>
+    <mergeCell ref="BB3:BD3"/>
+    <mergeCell ref="BE3:BG3"/>
+    <mergeCell ref="BH3:BJ3"/>
+    <mergeCell ref="BN3:BP3"/>
+    <mergeCell ref="BQ3:BS3"/>
+    <mergeCell ref="R3:T3"/>
+    <mergeCell ref="U3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="AA3:AC3"/>
+    <mergeCell ref="AD3:AF3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="O3:Q3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B5:B30">
